--- a/Res_ConvLSTM/DroughtDataset_model_testing_1754031464_individual_h_8.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1754031464_individual_h_8.xlsx
@@ -658,7 +658,7 @@
         <v>0.008490693911309379</v>
       </c>
       <c r="C2" t="n">
-        <v>50503824</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>50503824</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>35621166</v>
+        <v>4055298</v>
       </c>
       <c r="L2" t="n">
-        <v>20111925</v>
+        <v>1977519</v>
       </c>
       <c r="M2" t="n">
-        <v>4865315</v>
+        <v>409629</v>
       </c>
       <c r="N2" t="n">
-        <v>217213</v>
+        <v>7929</v>
       </c>
       <c r="O2" t="n">
-        <v>2917810</v>
+        <v>239190</v>
       </c>
       <c r="P2" t="n">
-        <v>1116550</v>
+        <v>87404</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999872446060181</v>
+        <v>0.9999946355819702</v>
       </c>
       <c r="R2" t="n">
-        <v>0.875677227973938</v>
+        <v>0.779538631439209</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7550851106643677</v>
+        <v>0.5949262976646423</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6958701014518738</v>
+        <v>0.4824068248271942</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3712763488292694</v>
+        <v>0.09612190723419189</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7449141144752502</v>
+        <v>0.5506545305252075</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8427523970603943</v>
+        <v>0.7023842930793762</v>
       </c>
       <c r="X2" t="n">
-        <v>50503824</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>50503824</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>38435590</v>
+        <v>4776143</v>
       </c>
       <c r="AG2" t="n">
-        <v>23824653</v>
+        <v>2997819</v>
       </c>
       <c r="AH2" t="n">
-        <v>6405435</v>
+        <v>803798</v>
       </c>
       <c r="AI2" t="n">
-        <v>472232</v>
+        <v>59153</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3675525</v>
+        <v>460411</v>
       </c>
       <c r="AK2" t="n">
-        <v>1440753</v>
+        <v>180245</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9562234282493591</v>
+        <v>0.9553927183151245</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9114547371864319</v>
+        <v>0.9118788242340088</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582150936126709</v>
+        <v>0.85825514793396</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6619678735733032</v>
+        <v>0.661193311214447</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020171165466309</v>
+        <v>0.9019849300384521</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314440488815308</v>
+        <v>0.9314650297164917</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002034640386319406</v>
       </c>
       <c r="C3" t="n">
-        <v>395</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>35621166</v>
+        <v>4055298</v>
       </c>
       <c r="E3" t="n">
-        <v>4413653</v>
+        <v>901179</v>
       </c>
       <c r="F3" t="n">
-        <v>92582</v>
+        <v>29086</v>
       </c>
       <c r="G3" t="n">
-        <v>6735</v>
+        <v>1449</v>
       </c>
       <c r="H3" t="n">
-        <v>5254</v>
+        <v>1600</v>
       </c>
       <c r="I3" t="n">
-        <v>188</v>
+        <v>61</v>
       </c>
       <c r="J3" t="n">
-        <v>80132332</v>
+        <v>10016588</v>
       </c>
       <c r="K3" t="n">
-        <v>85439573</v>
+        <v>10194037</v>
       </c>
       <c r="L3" t="n">
-        <v>97929553</v>
+        <v>11687235</v>
       </c>
       <c r="M3" t="n">
-        <v>121039597</v>
+        <v>14952153</v>
       </c>
       <c r="N3" t="n">
-        <v>129554910</v>
+        <v>16165436</v>
       </c>
       <c r="O3" t="n">
-        <v>125560495</v>
+        <v>15623523</v>
       </c>
       <c r="P3" t="n">
-        <v>128881343</v>
+        <v>16098975</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8874237537384033</v>
+        <v>0.8128993511199951</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7681037783622742</v>
+        <v>0.5999916195869446</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6512426137924194</v>
+        <v>0.4367326200008392</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3041947484016418</v>
+        <v>0.0884893536567688</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7156511545181274</v>
+        <v>0.468180239200592</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7216948866844177</v>
+        <v>0.4514902532100677</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>38435590</v>
+        <v>4776143</v>
       </c>
       <c r="Z3" t="n">
-        <v>1581425</v>
+        <v>197221</v>
       </c>
       <c r="AA3" t="n">
-        <v>68001</v>
+        <v>8441</v>
       </c>
       <c r="AB3" t="n">
-        <v>54459</v>
+        <v>6838</v>
       </c>
       <c r="AC3" t="n">
-        <v>258</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>240</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>80132976</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>88737218</v>
+        <v>11117918</v>
       </c>
       <c r="AG3" t="n">
-        <v>102138438</v>
+        <v>12743989</v>
       </c>
       <c r="AH3" t="n">
-        <v>122107746</v>
+        <v>15258909</v>
       </c>
       <c r="AI3" t="n">
-        <v>129681597</v>
+        <v>16209685</v>
       </c>
       <c r="AJ3" t="n">
-        <v>126160401</v>
+        <v>15768676</v>
       </c>
       <c r="AK3" t="n">
-        <v>128983636</v>
+        <v>16122748</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575390219688416</v>
+        <v>0.9573953747749329</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9098982810974121</v>
+        <v>0.909557044506073</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8573940396308899</v>
+        <v>0.8569823503494263</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6613346934318542</v>
+        <v>0.6601602435112</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9014958739280701</v>
+        <v>0.9011887311935425</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312471747398376</v>
+        <v>0.9310656785964966</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03209056867736627</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>4738046</v>
+        <v>1061570</v>
       </c>
       <c r="E4" t="n">
-        <v>20111925</v>
+        <v>1977519</v>
       </c>
       <c r="F4" t="n">
-        <v>1175322</v>
+        <v>218937</v>
       </c>
       <c r="G4" t="n">
-        <v>43888</v>
+        <v>9601</v>
       </c>
       <c r="H4" t="n">
-        <v>106462</v>
+        <v>26032</v>
       </c>
       <c r="I4" t="n">
-        <v>8217</v>
+        <v>2252</v>
       </c>
       <c r="J4" t="n">
-        <v>644</v>
+        <v>34</v>
       </c>
       <c r="K4" t="n">
-        <v>5057254</v>
+        <v>1146879</v>
       </c>
       <c r="L4" t="n">
-        <v>6523383</v>
+        <v>1346454</v>
       </c>
       <c r="M4" t="n">
-        <v>2126385</v>
+        <v>439507</v>
       </c>
       <c r="N4" t="n">
-        <v>367831</v>
+        <v>74560</v>
       </c>
       <c r="O4" t="n">
-        <v>999165</v>
+        <v>195184</v>
       </c>
       <c r="P4" t="n">
-        <v>208335</v>
+        <v>37035</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.999993622303009</v>
+        <v>0.9999973177909851</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8815113306045532</v>
+        <v>0.7958695292472839</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7615388035774231</v>
+        <v>0.5974482297897339</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6728171706199646</v>
+        <v>0.4584348797798157</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3344046175479889</v>
+        <v>0.09214784950017929</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7299894690513611</v>
+        <v>0.5060791969299316</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7775399088859558</v>
+        <v>0.5496605634689331</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1643061</v>
+        <v>208344</v>
       </c>
       <c r="Z4" t="n">
-        <v>23824653</v>
+        <v>2997819</v>
       </c>
       <c r="AA4" t="n">
-        <v>662423</v>
+        <v>82986</v>
       </c>
       <c r="AB4" t="n">
-        <v>44064</v>
+        <v>5563</v>
       </c>
       <c r="AC4" t="n">
-        <v>9119</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>544</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1759609</v>
+        <v>222998</v>
       </c>
       <c r="AG4" t="n">
-        <v>2314498</v>
+        <v>289700</v>
       </c>
       <c r="AH4" t="n">
-        <v>1058236</v>
+        <v>132751</v>
       </c>
       <c r="AI4" t="n">
-        <v>241144</v>
+        <v>30311</v>
       </c>
       <c r="AJ4" t="n">
-        <v>399259</v>
+        <v>50031</v>
       </c>
       <c r="AK4" t="n">
-        <v>106042</v>
+        <v>13262</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9568807482719421</v>
+        <v>0.9563930034637451</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106758832931519</v>
+        <v>0.9107164144515991</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578044176101685</v>
+        <v>0.8576182723045349</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6616511344909668</v>
+        <v>0.6606763601303101</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017564058303833</v>
+        <v>0.901586651802063</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313456416130066</v>
+        <v>0.9312652945518494</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>216481</v>
+        <v>61979</v>
       </c>
       <c r="E5" t="n">
-        <v>1770325</v>
+        <v>357223</v>
       </c>
       <c r="F5" t="n">
-        <v>4865315</v>
+        <v>409629</v>
       </c>
       <c r="G5" t="n">
-        <v>126560</v>
+        <v>22306</v>
       </c>
       <c r="H5" t="n">
-        <v>453312</v>
+        <v>77379</v>
       </c>
       <c r="I5" t="n">
-        <v>38806</v>
+        <v>9419</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>4518807</v>
+        <v>933386</v>
       </c>
       <c r="L5" t="n">
-        <v>6071939</v>
+        <v>1318392</v>
       </c>
       <c r="M5" t="n">
-        <v>2605503</v>
+        <v>528311</v>
       </c>
       <c r="N5" t="n">
-        <v>496846</v>
+        <v>81675</v>
       </c>
       <c r="O5" t="n">
-        <v>1159330</v>
+        <v>271703</v>
       </c>
       <c r="P5" t="n">
-        <v>430572</v>
+        <v>106186</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999950528144836</v>
+        <v>0.9999979138374329</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9266970753669739</v>
+        <v>0.8726077079772949</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9035851955413818</v>
+        <v>0.8368088603019714</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9637783169746399</v>
+        <v>0.9407323002815247</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9933810830116272</v>
+        <v>0.9904323816299438</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9834771156311035</v>
+        <v>0.9714085459709167</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9951092600822449</v>
+        <v>0.9912293553352356</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>64236</v>
+        <v>8050</v>
       </c>
       <c r="Z5" t="n">
-        <v>683114</v>
+        <v>86223</v>
       </c>
       <c r="AA5" t="n">
-        <v>6405435</v>
+        <v>803798</v>
       </c>
       <c r="AB5" t="n">
-        <v>79701</v>
+        <v>9997</v>
       </c>
       <c r="AC5" t="n">
-        <v>233268</v>
+        <v>29239</v>
       </c>
       <c r="AD5" t="n">
-        <v>5064</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1704383</v>
+        <v>212541</v>
       </c>
       <c r="AG5" t="n">
-        <v>2359211</v>
+        <v>298092</v>
       </c>
       <c r="AH5" t="n">
-        <v>1065383</v>
+        <v>134142</v>
       </c>
       <c r="AI5" t="n">
-        <v>241827</v>
+        <v>30451</v>
       </c>
       <c r="AJ5" t="n">
-        <v>401615</v>
+        <v>50482</v>
       </c>
       <c r="AK5" t="n">
-        <v>106369</v>
+        <v>13345</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734838008880615</v>
+        <v>0.9733282327651978</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642236232757568</v>
+        <v>0.9640045166015625</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837440848350525</v>
+        <v>0.9836558699607849</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963029623031616</v>
+        <v>0.9962790012359619</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938694834709167</v>
+        <v>0.993844747543335</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983740448951721</v>
+        <v>0.9983706474304199</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>101</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>92883</v>
+        <v>18220</v>
       </c>
       <c r="E6" t="n">
-        <v>147208</v>
+        <v>24062</v>
       </c>
       <c r="F6" t="n">
-        <v>176337</v>
+        <v>27926</v>
       </c>
       <c r="G6" t="n">
-        <v>217213</v>
+        <v>7929</v>
       </c>
       <c r="H6" t="n">
-        <v>74073</v>
+        <v>10289</v>
       </c>
       <c r="I6" t="n">
-        <v>6244</v>
+        <v>1167</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>51905</v>
+        <v>6568</v>
       </c>
       <c r="Z6" t="n">
-        <v>42831</v>
+        <v>5365</v>
       </c>
       <c r="AA6" t="n">
-        <v>87352</v>
+        <v>11023</v>
       </c>
       <c r="AB6" t="n">
-        <v>472232</v>
+        <v>59153</v>
       </c>
       <c r="AC6" t="n">
-        <v>55891</v>
+        <v>7014</v>
       </c>
       <c r="AD6" t="n">
-        <v>3848</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>9510</v>
+        <v>4993</v>
       </c>
       <c r="E7" t="n">
-        <v>178958</v>
+        <v>58619</v>
       </c>
       <c r="F7" t="n">
-        <v>641895</v>
+        <v>148587</v>
       </c>
       <c r="G7" t="n">
-        <v>174025</v>
+        <v>35368</v>
       </c>
       <c r="H7" t="n">
-        <v>2917810</v>
+        <v>239190</v>
       </c>
       <c r="I7" t="n">
-        <v>154880</v>
+        <v>24136</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>183</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>6480</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>237812</v>
+        <v>29968</v>
       </c>
       <c r="AB7" t="n">
-        <v>60794</v>
+        <v>7646</v>
       </c>
       <c r="AC7" t="n">
-        <v>3675525</v>
+        <v>460411</v>
       </c>
       <c r="AD7" t="n">
-        <v>96346</v>
+        <v>12050</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>334</v>
+        <v>117</v>
       </c>
       <c r="E8" t="n">
-        <v>13239</v>
+        <v>5371</v>
       </c>
       <c r="F8" t="n">
-        <v>40249</v>
+        <v>14971</v>
       </c>
       <c r="G8" t="n">
-        <v>16623</v>
+        <v>5836</v>
       </c>
       <c r="H8" t="n">
-        <v>360064</v>
+        <v>79884</v>
       </c>
       <c r="I8" t="n">
-        <v>1116550</v>
+        <v>87404</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>224</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>648</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2648</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2126</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>100723</v>
+        <v>12636</v>
       </c>
       <c r="AD8" t="n">
-        <v>1440753</v>
+        <v>180245</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
